--- a/artfynd/A 38115-2021 artfynd.xlsx
+++ b/artfynd/A 38115-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38115-2021 artfynd.xlsx
+++ b/artfynd/A 38115-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104153879</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546719.5794977417</v>
+        <v>546720</v>
       </c>
       <c r="R2" t="n">
-        <v>6858410.347076363</v>
+        <v>6858410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>104153880</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546754.0564167771</v>
+        <v>546754</v>
       </c>
       <c r="R3" t="n">
-        <v>6858447.641001207</v>
+        <v>6858448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,12 +890,7 @@
         <v>104153881</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546760.5436653214</v>
+        <v>546760</v>
       </c>
       <c r="R4" t="n">
-        <v>6858422.70923501</v>
+        <v>6858423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +959,9 @@
           <t>2021-11-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
